--- a/public/fixtures/clean_baseline.xlsx
+++ b/public/fixtures/clean_baseline.xlsx
@@ -53946,7 +53946,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>90265</t>
+          <t>94501</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -54215,7 +54215,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -54484,7 +54484,7 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>60007</t>
+          <t>62311</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -54769,7 +54769,7 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>98022</t>
+          <t>98832</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -55038,7 +55038,7 @@
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>77031</t>
+          <t>75751</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">

--- a/public/fixtures/clean_baseline.xlsx
+++ b/public/fixtures/clean_baseline.xlsx
@@ -53931,12 +53931,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>10/22/1991</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53976,7 +53976,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>04/08/2022</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54004,12 +54004,12 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$19.71</t>
+          <t>$18.94</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>$29.57</t>
+          <t>$28.41</t>
         </is>
       </c>
       <c r="U18" s="11" t="inlineStr">
@@ -54045,12 +54045,12 @@
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="inlineStr">
         <is>
-          <t>$19.13</t>
+          <t>$18.37</t>
         </is>
       </c>
       <c r="AC18" s="11" t="inlineStr">
         <is>
-          <t>$28.70</t>
+          <t>$27.55</t>
         </is>
       </c>
       <c r="AD18" s="11" t="inlineStr">
@@ -54070,18 +54070,18 @@
       </c>
       <c r="AG18" s="11" t="inlineStr">
         <is>
-          <t>$41,400.00</t>
+          <t>$39,800.00</t>
         </is>
       </c>
       <c r="AH18" s="11" t="n"/>
       <c r="AI18" s="11" t="inlineStr">
         <is>
-          <t>$18.56</t>
+          <t>$17.84</t>
         </is>
       </c>
       <c r="AJ18" s="11" t="inlineStr">
         <is>
-          <t>$27.84</t>
+          <t>$26.76</t>
         </is>
       </c>
       <c r="AK18" s="11" t="inlineStr">
@@ -54101,18 +54101,18 @@
       </c>
       <c r="AN18" s="11" t="inlineStr">
         <is>
-          <t>$40,100.00</t>
+          <t>$38,600.00</t>
         </is>
       </c>
       <c r="AO18" s="11" t="n"/>
       <c r="AP18" s="11" t="inlineStr">
         <is>
-          <t>$18.03</t>
+          <t>$17.31</t>
         </is>
       </c>
       <c r="AQ18" s="11" t="inlineStr">
         <is>
-          <t>$27.05</t>
+          <t>$25.96</t>
         </is>
       </c>
       <c r="AR18" s="11" t="inlineStr">
@@ -54132,7 +54132,7 @@
       </c>
       <c r="AU18" s="11" t="inlineStr">
         <is>
-          <t>$39,000.00</t>
+          <t>$37,500.00</t>
         </is>
       </c>
       <c r="AV18" s="11" t="inlineStr">
@@ -54200,7 +54200,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>09/05/1962</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54245,7 +54245,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>05/11/2023</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54273,12 +54273,12 @@
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$19.71</t>
+          <t>$18.94</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>$29.57</t>
+          <t>$28.41</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -54314,12 +54314,12 @@
       <c r="AA19" s="11" t="n"/>
       <c r="AB19" s="11" t="inlineStr">
         <is>
-          <t>$19.13</t>
+          <t>$18.37</t>
         </is>
       </c>
       <c r="AC19" s="11" t="inlineStr">
         <is>
-          <t>$28.70</t>
+          <t>$27.55</t>
         </is>
       </c>
       <c r="AD19" s="11" t="inlineStr">
@@ -54339,18 +54339,18 @@
       </c>
       <c r="AG19" s="11" t="inlineStr">
         <is>
-          <t>$41,400.00</t>
+          <t>$39,800.00</t>
         </is>
       </c>
       <c r="AH19" s="11" t="n"/>
       <c r="AI19" s="11" t="inlineStr">
         <is>
-          <t>$18.56</t>
+          <t>$17.84</t>
         </is>
       </c>
       <c r="AJ19" s="11" t="inlineStr">
         <is>
-          <t>$27.84</t>
+          <t>$26.76</t>
         </is>
       </c>
       <c r="AK19" s="11" t="inlineStr">
@@ -54370,18 +54370,18 @@
       </c>
       <c r="AN19" s="11" t="inlineStr">
         <is>
-          <t>$40,100.00</t>
+          <t>$38,600.00</t>
         </is>
       </c>
       <c r="AO19" s="11" t="n"/>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>$18.03</t>
+          <t>$17.31</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>$27.05</t>
+          <t>$25.96</t>
         </is>
       </c>
       <c r="AR19" s="11" t="inlineStr">
@@ -54401,7 +54401,7 @@
       </c>
       <c r="AU19" s="11" t="inlineStr">
         <is>
-          <t>$39,000.00</t>
+          <t>$37,500.00</t>
         </is>
       </c>
       <c r="AV19" s="11" t="inlineStr">
@@ -54469,7 +54469,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>05/05/1982</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54514,7 +54514,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>01/02/2020</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54546,12 +54546,12 @@
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$35.62</t>
+          <t>$34.18</t>
         </is>
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>$53.43</t>
+          <t>$51.27</t>
         </is>
       </c>
       <c r="U20" s="11" t="inlineStr">
@@ -54591,12 +54591,12 @@
       </c>
       <c r="AB20" s="11" t="inlineStr">
         <is>
-          <t>$34.57</t>
+          <t>$33.17</t>
         </is>
       </c>
       <c r="AC20" s="11" t="inlineStr">
         <is>
-          <t>$51.86</t>
+          <t>$49.76</t>
         </is>
       </c>
       <c r="AD20" s="11" t="inlineStr">
@@ -54626,12 +54626,12 @@
       </c>
       <c r="AI20" s="11" t="inlineStr">
         <is>
-          <t>$33.56</t>
+          <t>$32.21</t>
         </is>
       </c>
       <c r="AJ20" s="11" t="inlineStr">
         <is>
-          <t>$50.34</t>
+          <t>$48.31</t>
         </is>
       </c>
       <c r="AK20" s="11" t="inlineStr">
@@ -54661,12 +54661,12 @@
       </c>
       <c r="AP20" s="11" t="inlineStr">
         <is>
-          <t>$32.60</t>
+          <t>$31.30</t>
         </is>
       </c>
       <c r="AQ20" s="11" t="inlineStr">
         <is>
-          <t>$48.90</t>
+          <t>$46.95</t>
         </is>
       </c>
       <c r="AR20" s="11" t="inlineStr">
@@ -54754,7 +54754,7 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>03/19/1976</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -54799,7 +54799,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>11/25/2020</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -54827,12 +54827,12 @@
       <c r="R21" s="14" t="n"/>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$17.31</t>
+          <t>$16.63</t>
         </is>
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>$25.96</t>
+          <t>$24.95</t>
         </is>
       </c>
       <c r="U21" s="11" t="inlineStr">
@@ -54868,12 +54868,12 @@
       <c r="AA21" s="11" t="n"/>
       <c r="AB21" s="11" t="inlineStr">
         <is>
-          <t>$16.83</t>
+          <t>$16.15</t>
         </is>
       </c>
       <c r="AC21" s="11" t="inlineStr">
         <is>
-          <t>$25.24</t>
+          <t>$24.22</t>
         </is>
       </c>
       <c r="AD21" s="11" t="inlineStr">
@@ -54893,18 +54893,18 @@
       </c>
       <c r="AG21" s="11" t="inlineStr">
         <is>
-          <t>$36,400.00</t>
+          <t>$35,000.00</t>
         </is>
       </c>
       <c r="AH21" s="11" t="n"/>
       <c r="AI21" s="11" t="inlineStr">
         <is>
-          <t>$16.35</t>
+          <t>$15.67</t>
         </is>
       </c>
       <c r="AJ21" s="11" t="inlineStr">
         <is>
-          <t>$24.53</t>
+          <t>$23.50</t>
         </is>
       </c>
       <c r="AK21" s="11" t="inlineStr">
@@ -54924,18 +54924,18 @@
       </c>
       <c r="AN21" s="11" t="inlineStr">
         <is>
-          <t>$35,400.00</t>
+          <t>$34,000.00</t>
         </is>
       </c>
       <c r="AO21" s="11" t="n"/>
       <c r="AP21" s="11" t="inlineStr">
         <is>
-          <t>$15.87</t>
+          <t>$15.24</t>
         </is>
       </c>
       <c r="AQ21" s="11" t="inlineStr">
         <is>
-          <t>$23.80</t>
+          <t>$22.86</t>
         </is>
       </c>
       <c r="AR21" s="11" t="inlineStr">
@@ -54955,7 +54955,7 @@
       </c>
       <c r="AU21" s="11" t="inlineStr">
         <is>
-          <t>$34,300.00</t>
+          <t>$33,000.00</t>
         </is>
       </c>
       <c r="AV21" s="11" t="inlineStr">
@@ -55023,12 +55023,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>10/02/1987</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -55068,7 +55068,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>09/20/2012</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
@@ -55104,12 +55104,12 @@
       <c r="R22" s="14" t="n"/>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$16.73</t>
+          <t>$16.06</t>
         </is>
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>$25.09</t>
+          <t>$24.09</t>
         </is>
       </c>
       <c r="U22" s="11" t="inlineStr">
@@ -55145,12 +55145,12 @@
       <c r="AA22" s="11" t="n"/>
       <c r="AB22" s="11" t="inlineStr">
         <is>
-          <t>$16.25</t>
+          <t>$15.58</t>
         </is>
       </c>
       <c r="AC22" s="11" t="inlineStr">
         <is>
-          <t>$24.38</t>
+          <t>$23.37</t>
         </is>
       </c>
       <c r="AD22" s="11" t="inlineStr">
@@ -55170,18 +55170,18 @@
       </c>
       <c r="AG22" s="11" t="inlineStr">
         <is>
-          <t>$35,200.00</t>
+          <t>$33,800.00</t>
         </is>
       </c>
       <c r="AH22" s="11" t="n"/>
       <c r="AI22" s="11" t="inlineStr">
         <is>
-          <t>$15.77</t>
+          <t>$15.14</t>
         </is>
       </c>
       <c r="AJ22" s="11" t="inlineStr">
         <is>
-          <t>$23.66</t>
+          <t>$22.71</t>
         </is>
       </c>
       <c r="AK22" s="11" t="inlineStr">
@@ -55201,18 +55201,18 @@
       </c>
       <c r="AN22" s="11" t="inlineStr">
         <is>
-          <t>$34,100.00</t>
+          <t>$32,800.00</t>
         </is>
       </c>
       <c r="AO22" s="11" t="n"/>
       <c r="AP22" s="11" t="inlineStr">
         <is>
-          <t>$15.29</t>
+          <t>$14.66</t>
         </is>
       </c>
       <c r="AQ22" s="11" t="inlineStr">
         <is>
-          <t>$22.93</t>
+          <t>$21.99</t>
         </is>
       </c>
       <c r="AR22" s="11" t="inlineStr">
@@ -55232,7 +55232,7 @@
       </c>
       <c r="AU22" s="11" t="inlineStr">
         <is>
-          <t>$33,100.00</t>
+          <t>$31,800.00</t>
         </is>
       </c>
       <c r="AV22" s="11" t="inlineStr">

--- a/public/fixtures/clean_baseline.xlsx
+++ b/public/fixtures/clean_baseline.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Census Template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Census Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROVENANCE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
@@ -33,6 +33,7 @@
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26"/>
   </externalReferences>
   <definedNames>
     <definedName name="_____dc1" hidden="1">{#N/A,#N/A,FALSE,"COVER PAGE";#N/A,#N/A,FALSE,"HIGHLITES";#N/A,#N/A,FALSE,"INC STATE (1)";#N/A,#N/A,FALSE,"DPC BY DEPT";#N/A,#N/A,FALSE,"FIXED COSTS";#N/A,#N/A,FALSE,"PRODUCTION";#N/A,#N/A,FALSE,"SALES TRND";#N/A,#N/A,FALSE,"BALANCE SHEET";#N/A,#N/A,FALSE,"INVENTORY";#N/A,#N/A,FALSE,"MFG VAR";#N/A,#N/A,FALSE,"OVRHD SPND";#N/A,#N/A,FALSE,"ENERGY COSTS";#N/A,#N/A,FALSE,"MAINTENANCE";#N/A,#N/A,FALSE,"LABOR";#N/A,#N/A,FALSE,"ACTVSFORECAST"}</definedName>
@@ -53931,12 +53932,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>10/22/1991</t>
+          <t>05/13/1970</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53976,7 +53977,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>04/08/2022</t>
+          <t>06/14/2023</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54200,12 +54201,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>09/05/1962</t>
+          <t>12/04/1997</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54245,7 +54246,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>05/11/2023</t>
+          <t>09/20/2014</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54469,7 +54470,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>05/05/1982</t>
+          <t>03/07/1992</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54514,7 +54515,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>01/02/2020</t>
+          <t>09/21/2014</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54754,12 +54755,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>03/19/1976</t>
+          <t>02/10/1987</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54799,7 +54800,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>11/25/2020</t>
+          <t>06/13/2019</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55023,12 +55024,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>10/02/1987</t>
+          <t>09/17/1998</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -55068,7 +55069,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>09/20/2012</t>
+          <t>07/15/2024</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
@@ -62737,4 +62738,471 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nine Dean — simulated census: data provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>generated 2026-07-20 00:01 from the reference warehouse (public.ext_*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>warehouse table</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vintage</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MIT · Living Wage Calculator</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ext_mit_expense</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>301,824</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>mit:livingwage.mit.edu:2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Engine A basket components</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MIT · Living Wage Calculator</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ext_mit_living_wage</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>113,184</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>mit:livingwage.mit.edu:2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Engine A living-wage reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EPI · Family Budget Calculator</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ext_epi_cost</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>502,880</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>epi:2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Engine A basket (food, childcare, medical, housing, other)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EPI · Family Budget Calculator</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ext_epi_county</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3,143</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>epi:2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Engine A county coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACS · B25064 median gross rent</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ext_acs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3,222</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>acs:5y2023-B25064</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Engine A housing candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CNT · H+T Affordability Index</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ext_cnt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3,144</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cnt:2022</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Engine A transportation (override, not MAX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BLS OEWS · state wages</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ext_bls_oews_state_wage</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>35,427</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>May2024</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>wages by state+SOC (p10/p25/median); prevailing-wage overlay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>O*NET · SOC occupations</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ext_onet_soc_occupation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1,016</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>O*NET 29.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>job titles and SOC codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>O*NET · SOC alternate titles</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ext_onet_soc_alt_title</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>55,119</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>O*NET 29.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>title → SOC matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Census · ZCTA↔county crosswalk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ext_census_zcta_county</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>23,355</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>census_zcta:2020</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>residence ZIP → county</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Census · county gazetteer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ext_census_county</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3,222</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>census_county:2024</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>county names / states</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A Better Balance · PSL statutes</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ext_abb_psl_law</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>abb:2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Engine B floors (cap / preempted / no-cap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KFF · EHBS benchmarks</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ext_kff_ehbs_health_benchmarks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>kff_ehbs:2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Engine C employer-contribution thresholds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Peterson-KFF · OOP cost-sharing</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ext_peterson_kff_oop_costsharing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>live scrape; page modified 2026-02-11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Engine C out-of-pocket exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PolicyEngine US</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>in-process library (not a warehouse table)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>policyengine-us 1.745.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Engine A federal + state + payroll + local tax</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/fixtures/clean_baseline.xlsx
+++ b/public/fixtures/clean_baseline.xlsx
@@ -53932,12 +53932,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>05/13/1970</t>
+          <t>02/22/1963</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53977,7 +53977,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>06/14/2023</t>
+          <t>10/16/2017</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54201,7 +54201,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>12/04/1997</t>
+          <t>04/04/1993</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54246,7 +54246,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>09/20/2014</t>
+          <t>11/24/2025</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54470,7 +54470,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>03/07/1992</t>
+          <t>01/13/1966</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54515,7 +54515,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>09/21/2014</t>
+          <t>06/03/2020</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54755,12 +54755,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>02/10/1987</t>
+          <t>03/27/1972</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54800,7 +54800,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>06/13/2019</t>
+          <t>07/10/2016</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55024,7 +55024,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>09/17/1998</t>
+          <t>01/09/1970</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -55069,7 +55069,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>07/15/2024</t>
+          <t>07/01/2024</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
@@ -62766,7 +62766,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 00:01 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 00:25 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/clean_baseline.xlsx
+++ b/public/fixtures/clean_baseline.xlsx
@@ -53932,12 +53932,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>02/22/1963</t>
+          <t>07/03/1968</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53977,7 +53977,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>10/16/2017</t>
+          <t>12/10/2014</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54201,12 +54201,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>04/04/1993</t>
+          <t>11/11/1980</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54246,7 +54246,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>11/24/2025</t>
+          <t>10/04/2019</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54470,12 +54470,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>01/13/1966</t>
+          <t>12/20/2001</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54515,7 +54515,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>06/03/2020</t>
+          <t>04/26/2022</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54755,7 +54755,7 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>03/27/1972</t>
+          <t>01/01/1966</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -54800,7 +54800,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>07/10/2016</t>
+          <t>11/13/2013</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55024,12 +55024,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>01/09/1970</t>
+          <t>02/14/1967</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -55069,7 +55069,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>07/01/2024</t>
+          <t>07/04/2020</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
@@ -62766,7 +62766,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 00:25 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 12:56 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/clean_baseline.xlsx
+++ b/public/fixtures/clean_baseline.xlsx
@@ -53075,7 +53075,11 @@
           <t>Company Name:</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n"/>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>Cedar Ridge Manufacturing, Inc.</t>
+        </is>
+      </c>
       <c r="C8" s="46" t="n"/>
       <c r="D8" s="46" t="n"/>
       <c r="E8" s="45" t="n"/>
@@ -53140,7 +53144,11 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="B9" s="43" t="n"/>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>07/20/2026</t>
+        </is>
+      </c>
       <c r="C9" s="43" t="n"/>
       <c r="D9" s="43" t="n"/>
       <c r="E9" s="43" t="n"/>
@@ -53932,7 +53940,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>07/03/1968</t>
+          <t>03/15/1976</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53977,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>12/10/2014</t>
+          <t>09/01/2014</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54201,7 +54209,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>11/11/1980</t>
+          <t>05/01/1994</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54246,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>10/04/2019</t>
+          <t>04/07/2013</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54470,12 +54478,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>12/20/2001</t>
+          <t>05/05/1998</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54515,7 +54523,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>04/26/2022</t>
+          <t>12/18/2018</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54755,12 +54763,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>01/01/1966</t>
+          <t>02/02/1999</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54800,7 +54808,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>11/13/2013</t>
+          <t>06/09/2022</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55024,7 +55032,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>02/14/1967</t>
+          <t>08/28/1981</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -55069,7 +55077,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>07/04/2020</t>
+          <t>07/21/2024</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
@@ -62766,7 +62774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 12:56 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 18:19 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/clean_baseline.xlsx
+++ b/public/fixtures/clean_baseline.xlsx
@@ -53940,7 +53940,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>03/15/1976</t>
+          <t>09/21/1974</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>09/01/2014</t>
+          <t>06/04/2013</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54209,12 +54209,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>05/01/1994</t>
+          <t>08/12/1989</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54254,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>04/07/2013</t>
+          <t>06/01/2021</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54478,12 +54478,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>05/05/1998</t>
+          <t>04/24/1997</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54523,7 +54523,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>12/18/2018</t>
+          <t>12/06/2018</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54763,12 +54763,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>02/02/1999</t>
+          <t>07/27/1996</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54808,7 +54808,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>06/09/2022</t>
+          <t>03/07/2021</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55032,7 +55032,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>08/28/1981</t>
+          <t>08/08/1989</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -55077,7 +55077,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>07/21/2024</t>
+          <t>04/19/2021</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
@@ -62774,7 +62774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 18:19 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 19:46 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/clean_baseline.xlsx
+++ b/public/fixtures/clean_baseline.xlsx
@@ -53146,7 +53146,7 @@
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>07/20/2026</t>
+          <t>07/21/2026</t>
         </is>
       </c>
       <c r="C9" s="43" t="n"/>
@@ -53940,12 +53940,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>09/21/1974</t>
+          <t>08/12/1981</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>06/04/2013</t>
+          <t>03/04/2013</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54209,7 +54209,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>08/12/1989</t>
+          <t>12/12/1997</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54254,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>06/01/2021</t>
+          <t>05/26/2021</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54478,7 +54478,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>04/24/1997</t>
+          <t>08/24/1985</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54523,7 +54523,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>12/06/2018</t>
+          <t>02/06/2019</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54763,7 +54763,7 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>07/27/1996</t>
+          <t>03/03/2000</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -54808,7 +54808,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>03/07/2021</t>
+          <t>01/19/2019</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55032,12 +55032,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>08/08/1989</t>
+          <t>07/07/1992</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -55077,7 +55077,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>04/19/2021</t>
+          <t>02/28/2013</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
@@ -62774,7 +62774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 19:46 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-21 18:04 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/clean_baseline.xlsx
+++ b/public/fixtures/clean_baseline.xlsx
@@ -53146,7 +53146,7 @@
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>07/21/2026</t>
+          <t>07/22/2026</t>
         </is>
       </c>
       <c r="C9" s="43" t="n"/>
@@ -53940,12 +53940,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>08/12/1981</t>
+          <t>09/01/1970</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>03/04/2013</t>
+          <t>06/18/2013</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54209,12 +54209,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>12/12/1997</t>
+          <t>11/23/1988</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54254,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>05/26/2021</t>
+          <t>03/10/2014</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54478,12 +54478,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>08/24/1985</t>
+          <t>03/07/1988</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54523,7 +54523,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>02/06/2019</t>
+          <t>12/25/2022</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54763,12 +54763,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>03/03/2000</t>
+          <t>12/20/1969</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54808,7 +54808,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>01/19/2019</t>
+          <t>07/27/2016</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55032,7 +55032,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>07/07/1992</t>
+          <t>09/21/1990</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -55077,7 +55077,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>02/28/2013</t>
+          <t>06/06/2024</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
@@ -62774,7 +62774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-21 18:04 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-22 14:38 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>
